--- a/spark-cv/data/research.xlsx
+++ b/spark-cv/data/research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEEDE8C-B49F-480F-A5AD-B5C397DC503B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E996316A-2091-40DD-AFA9-7F596843496C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="1605" windowWidth="24735" windowHeight="11820" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
   <si>
     <t>type</t>
   </si>
@@ -148,6 +148,21 @@
   </si>
   <si>
     <t>Contributed to enhancing SWAT+ simulation of groundwater flow and groundwater-surface water interactions using MODFLOW routines</t>
+  </si>
+  <si>
+    <t>teaching</t>
+  </si>
+  <si>
+    <t>Created lesson plans and trained people on software programs like Excel, Word, Access, Outlook, and PowerPoint by doing hands-on demonstrations and providing one-on-one application support.</t>
+  </si>
+  <si>
+    <t>Provided undergraduate students with a broad introduction into 2-dimensional and 3-dimensional Computer-Aided Design (CAD) with a focus on construction and architecture-specific applications including environmental infrastructure</t>
+  </si>
+  <si>
+    <t>AutoCAD</t>
+  </si>
+  <si>
+    <t>Taught an industry-leading CAD software program (Autodesk AutoCAD) to model construction projects and then create and distribute basic, industry-standard architectural drawings</t>
   </si>
 </sst>
 </file>
@@ -533,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80AB2D6-D787-8D4A-BD11-32CAE09CA316}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="11" style="3"/>
@@ -579,7 +594,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -599,7 +614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -660,7 +675,7 @@
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -889,7 +904,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1">
         <v>2018</v>
@@ -908,6 +923,72 @@
       </c>
       <c r="J16" s="5" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2011</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2012</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2004</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2006</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2004</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2006</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/spark-cv/data/research.xlsx
+++ b/spark-cv/data/research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E996316A-2091-40DD-AFA9-7F596843496C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C046C37-1052-4E88-9E85-B60392AB6664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
+    <workbookView xWindow="4200" yWindow="3120" windowWidth="21600" windowHeight="11505" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="70">
   <si>
     <t>type</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Python, PEST</t>
   </si>
   <si>
-    <t>https://github.com/spark-brc/apexmf</t>
-  </si>
-  <si>
     <t>https://github.com/spark-brc/swatmf</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>Fortran</t>
   </si>
   <si>
-    <t>Contribute SWAT-MODFLOW</t>
-  </si>
-  <si>
     <t>Assessed Surface Water and Groundwater Resources in the Middle Bosque, Texas Watershed using the coupled SWAT-MODFLOW model</t>
   </si>
   <si>
@@ -163,6 +157,84 @@
   </si>
   <si>
     <t>Taught an industry-leading CAD software program (Autodesk AutoCAD) to model construction projects and then create and distribute basic, industry-standard architectural drawings</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW, PEST</t>
+  </si>
+  <si>
+    <t>MODFLOW</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>APEXMOD</t>
+  </si>
+  <si>
+    <t>QSWATMOD</t>
+  </si>
+  <si>
+    <t>APEX-CUT</t>
+  </si>
+  <si>
+    <t>Contributed to enhancing SWAT-MODFLOW</t>
+  </si>
+  <si>
+    <t>SWAT+MODFLOW</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW</t>
+  </si>
+  <si>
+    <t>APEX-MODFLOW</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/APEXMOD</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/QSWATMOD2</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/APEXCUTE</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/SWAT-MODFLOW3</t>
+  </si>
+  <si>
+    <t>https://epicapex.tamu.edu/</t>
+  </si>
+  <si>
+    <t>https://swat.tamu.edu/software/swat-modflow/</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>https://share.streamlit.io/spark-brc/crb_apexmf/main/main.py</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/crb_apexmf</t>
+  </si>
+  <si>
+    <t>https://share.streamlit.io/spark-brc/apex-viz/main/main.py</t>
+  </si>
+  <si>
+    <t>https://share.streamlit.io/spark-brc/apexmf-viz/main/main.py</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/apex-viz</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/apexmf-viz</t>
+  </si>
+  <si>
+    <t>Develop a web application for visualizing and analyzing Colorado River Basin (CRB) APEX-MODFLOW model performance</t>
+  </si>
+  <si>
+    <t>Develop a web application for visualizing and analyzing Biomass in grazing lands</t>
+  </si>
+  <si>
+    <t>Develop a web application for visualizing and analyzing APEX simulation results</t>
   </si>
 </sst>
 </file>
@@ -548,21 +620,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80AB2D6-D787-8D4A-BD11-32CAE09CA316}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="11" style="3"/>
     <col min="4" max="4" width="23.5" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.5" style="3" customWidth="1"/>
     <col min="6" max="6" width="62" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11" style="3"/>
-    <col min="9" max="9" width="26.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="23.875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="11" style="3"/>
+    <col min="7" max="8" width="25.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="26.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.875" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="11" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -585,16 +657,19 @@
         <v>8</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="K1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -614,7 +689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -634,7 +709,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -653,11 +728,11 @@
       <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="J4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -671,11 +746,14 @@
         <v>2020</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" ht="63" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -692,13 +770,13 @@
         <v>2019</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -715,10 +793,13 @@
         <v>2018</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -735,10 +816,13 @@
         <v>2018</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -755,12 +839,15 @@
         <v>2018</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -775,17 +862,23 @@
         <v>2021</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
@@ -800,17 +893,20 @@
         <v>2020</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -821,34 +917,56 @@
       <c r="D12" s="2">
         <v>2019</v>
       </c>
+      <c r="E12" s="2">
+        <v>2017</v>
+      </c>
       <c r="F12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
       </c>
       <c r="D13" s="1">
         <v>2020</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -860,22 +978,28 @@
         <v>2020</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2">
         <v>2018</v>
@@ -884,27 +1008,31 @@
         <v>2019</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1">
         <v>2018</v>
@@ -913,94 +1041,185 @@
         <v>2019</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2012</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2004</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2006</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2011</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2012</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="3">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3">
+    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3">
         <v>2004</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E22" s="3">
         <v>2006</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="3">
-        <v>3</v>
-      </c>
-      <c r="D19" s="3">
-        <v>2004</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2006</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>44</v>
+      <c r="G22" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I4" r:id="rId1" xr:uid="{DCC76F9B-3E7E-4171-97CA-40E76F1BA6F9}"/>
-    <hyperlink ref="I16" r:id="rId2" xr:uid="{DF4C2ACF-C936-43F8-8A2C-BDE02ABB3CF6}"/>
-    <hyperlink ref="J16" r:id="rId3" xr:uid="{441A2F84-E160-4555-8500-D4D34A2FC107}"/>
-    <hyperlink ref="I15" r:id="rId4" xr:uid="{F9EEFC00-AFD8-4BE5-B5A3-A6724CA68C0C}"/>
-    <hyperlink ref="J15" r:id="rId5" xr:uid="{10A45DE1-5D56-4F7E-B0FD-85BAA1CDA6C5}"/>
-    <hyperlink ref="I14" r:id="rId6" xr:uid="{14BEFD48-CC80-413C-AD88-7DB68B91474E}"/>
+    <hyperlink ref="J4" r:id="rId1" xr:uid="{DCC76F9B-3E7E-4171-97CA-40E76F1BA6F9}"/>
+    <hyperlink ref="J16" r:id="rId2" xr:uid="{DF4C2ACF-C936-43F8-8A2C-BDE02ABB3CF6}"/>
+    <hyperlink ref="K16" r:id="rId3" xr:uid="{441A2F84-E160-4555-8500-D4D34A2FC107}"/>
+    <hyperlink ref="J15" r:id="rId4" xr:uid="{F9EEFC00-AFD8-4BE5-B5A3-A6724CA68C0C}"/>
+    <hyperlink ref="J14" r:id="rId5" xr:uid="{14BEFD48-CC80-413C-AD88-7DB68B91474E}"/>
+    <hyperlink ref="J13" r:id="rId6" xr:uid="{4ECEA80F-0B5F-430D-AAFC-CCC038B99925}"/>
+    <hyperlink ref="J12" r:id="rId7" xr:uid="{2A24C6D0-7C63-402C-A51A-E6DB052AD448}"/>
+    <hyperlink ref="I10" r:id="rId8" xr:uid="{F6080946-475C-428D-B199-C2AD3F8870D3}"/>
+    <hyperlink ref="I12" r:id="rId9" xr:uid="{FE0A1123-E816-4929-A241-93305BE61363}"/>
+    <hyperlink ref="I15" r:id="rId10" xr:uid="{91BDAB47-14B9-4A56-AD0A-1A6EB8488A7C}"/>
+    <hyperlink ref="J17" r:id="rId11" xr:uid="{7BD9F0C1-6F50-409D-8E77-76062676D3EC}"/>
+    <hyperlink ref="I17" r:id="rId12" xr:uid="{437E220B-63F3-4E00-844A-7CF1B055C39A}"/>
+    <hyperlink ref="J19" r:id="rId13" xr:uid="{273DDD2C-2A65-4892-8D7B-DAB407A1825C}"/>
+    <hyperlink ref="I19" r:id="rId14" xr:uid="{86E05EFD-83D2-4FDF-AF6A-74CD19D2E237}"/>
+    <hyperlink ref="J18" r:id="rId15" xr:uid="{5787F73E-5394-46BA-9912-DEFCCBF121E6}"/>
+    <hyperlink ref="I18" r:id="rId16" xr:uid="{AD191B46-2F27-4B87-B375-8ECF2EF3C755}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>
--- a/spark-cv/data/research.xlsx
+++ b/spark-cv/data/research.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C046C37-1052-4E88-9E85-B60392AB6664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9211C184-4FF3-4CD7-B4E5-50A8AB192770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="3120" windowWidth="21600" windowHeight="11505" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
+    <workbookView xWindow="51480" yWindow="3300" windowWidth="29040" windowHeight="17790" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="79">
   <si>
     <t>type</t>
   </si>
@@ -39,9 +39,6 @@
     <t>repo</t>
   </si>
   <si>
-    <t>mp</t>
-  </si>
-  <si>
     <t>what</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>Develop SWAT-MODFLOW model to support resilient development and return on investment analyses in the Cubango-Okavango River Basin (CORB)</t>
   </si>
   <si>
-    <t>Develop a graphical user interface, a workflow implemented in QGIS, for application and evaluation of APEX-MODFLOW models</t>
-  </si>
-  <si>
     <t xml:space="preserve">Contribute to the development of APEX model optimization tool </t>
   </si>
   <si>
@@ -235,6 +229,39 @@
   </si>
   <si>
     <t>Develop a web application for visualizing and analyzing APEX simulation results</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>Develop Python code for optimizing the DAYCENT model using the Bayesian method with the Differential Evolution Adaptive Metropolis (DREAM) algorithm</t>
+  </si>
+  <si>
+    <t>DayCentPy</t>
+  </si>
+  <si>
+    <t>https://github.com/spark-brc/daycentpy</t>
+  </si>
+  <si>
+    <t>Developed a graphical user interface, a workflow implemented in QGIS, for application and evaluation of APEX-MODFLOW models</t>
+  </si>
+  <si>
+    <t>Develop a Carbon dynamics model for predicting GHG emission and sequestration in croplands</t>
+  </si>
+  <si>
+    <t>Fortran, Python</t>
+  </si>
+  <si>
+    <t>SWAT+GHG</t>
+  </si>
+  <si>
+    <t>committee</t>
+  </si>
+  <si>
+    <t>Fall 2023</t>
+  </si>
+  <si>
+    <t>Member, Graduate Committee, Ali Akram Niazi from Parkistan, Ph.D program in Biological and Agricultural Engineering (BAEN), Texas A&amp;M University, College Station, TX, Admitted to the BAEN graduate school to start the first semester in Fall 2015. Chair: Clyde Munster (BAEN)</t>
   </si>
 </sst>
 </file>
@@ -285,12 +312,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -620,329 +644,265 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80AB2D6-D787-8D4A-BD11-32CAE09CA316}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="11" style="3"/>
-    <col min="4" max="4" width="23.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="62" style="3" customWidth="1"/>
-    <col min="7" max="8" width="25.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18.875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="26.75" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23.875" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="11" style="3"/>
+    <col min="1" max="3" width="11" style="2"/>
+    <col min="4" max="4" width="23.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="62" style="2" customWidth="1"/>
+    <col min="7" max="8" width="25.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="3" t="s">
+    </row>
+    <row r="5" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2020</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="D8" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2019</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2017</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2018</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2017</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2018</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="D11" s="2">
+        <v>2015</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2018</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2020</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2020</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2020</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" ht="63" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2018</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2019</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2017</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2018</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2017</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2018</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="3">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2015</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2018</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2020</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2017</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="6"/>
+      <c r="D12" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
@@ -950,276 +910,415 @@
       <c r="D13" s="1">
         <v>2020</v>
       </c>
+      <c r="E13" s="1">
+        <v>2021</v>
+      </c>
       <c r="F13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>2020</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E15" s="2">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2019</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J15" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="J21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2012</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2">
         <v>2</v>
       </c>
-      <c r="D16" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" ht="63" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="D25" s="2">
+        <v>2004</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2006</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2004</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2006</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2012</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="63" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="3">
-        <v>2</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2004</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2006</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="3">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2004</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2006</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>42</v>
+      <c r="D27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J4" r:id="rId1" xr:uid="{DCC76F9B-3E7E-4171-97CA-40E76F1BA6F9}"/>
-    <hyperlink ref="J16" r:id="rId2" xr:uid="{DF4C2ACF-C936-43F8-8A2C-BDE02ABB3CF6}"/>
-    <hyperlink ref="K16" r:id="rId3" xr:uid="{441A2F84-E160-4555-8500-D4D34A2FC107}"/>
-    <hyperlink ref="J15" r:id="rId4" xr:uid="{F9EEFC00-AFD8-4BE5-B5A3-A6724CA68C0C}"/>
-    <hyperlink ref="J14" r:id="rId5" xr:uid="{14BEFD48-CC80-413C-AD88-7DB68B91474E}"/>
-    <hyperlink ref="J13" r:id="rId6" xr:uid="{4ECEA80F-0B5F-430D-AAFC-CCC038B99925}"/>
-    <hyperlink ref="J12" r:id="rId7" xr:uid="{2A24C6D0-7C63-402C-A51A-E6DB052AD448}"/>
-    <hyperlink ref="I10" r:id="rId8" xr:uid="{F6080946-475C-428D-B199-C2AD3F8870D3}"/>
-    <hyperlink ref="I12" r:id="rId9" xr:uid="{FE0A1123-E816-4929-A241-93305BE61363}"/>
-    <hyperlink ref="I15" r:id="rId10" xr:uid="{91BDAB47-14B9-4A56-AD0A-1A6EB8488A7C}"/>
-    <hyperlink ref="J17" r:id="rId11" xr:uid="{7BD9F0C1-6F50-409D-8E77-76062676D3EC}"/>
-    <hyperlink ref="I17" r:id="rId12" xr:uid="{437E220B-63F3-4E00-844A-7CF1B055C39A}"/>
-    <hyperlink ref="J19" r:id="rId13" xr:uid="{273DDD2C-2A65-4892-8D7B-DAB407A1825C}"/>
-    <hyperlink ref="I19" r:id="rId14" xr:uid="{86E05EFD-83D2-4FDF-AF6A-74CD19D2E237}"/>
-    <hyperlink ref="J18" r:id="rId15" xr:uid="{5787F73E-5394-46BA-9912-DEFCCBF121E6}"/>
-    <hyperlink ref="I18" r:id="rId16" xr:uid="{AD191B46-2F27-4B87-B375-8ECF2EF3C755}"/>
+    <hyperlink ref="J6" r:id="rId1" xr:uid="{DCC76F9B-3E7E-4171-97CA-40E76F1BA6F9}"/>
+    <hyperlink ref="J20" r:id="rId2" xr:uid="{DF4C2ACF-C936-43F8-8A2C-BDE02ABB3CF6}"/>
+    <hyperlink ref="K20" r:id="rId3" xr:uid="{441A2F84-E160-4555-8500-D4D34A2FC107}"/>
+    <hyperlink ref="J19" r:id="rId4" xr:uid="{F9EEFC00-AFD8-4BE5-B5A3-A6724CA68C0C}"/>
+    <hyperlink ref="J18" r:id="rId5" xr:uid="{14BEFD48-CC80-413C-AD88-7DB68B91474E}"/>
+    <hyperlink ref="J17" r:id="rId6" xr:uid="{4ECEA80F-0B5F-430D-AAFC-CCC038B99925}"/>
+    <hyperlink ref="J15" r:id="rId7" xr:uid="{2A24C6D0-7C63-402C-A51A-E6DB052AD448}"/>
+    <hyperlink ref="I13" r:id="rId8" xr:uid="{F6080946-475C-428D-B199-C2AD3F8870D3}"/>
+    <hyperlink ref="I15" r:id="rId9" xr:uid="{FE0A1123-E816-4929-A241-93305BE61363}"/>
+    <hyperlink ref="I19" r:id="rId10" xr:uid="{91BDAB47-14B9-4A56-AD0A-1A6EB8488A7C}"/>
+    <hyperlink ref="J21" r:id="rId11" xr:uid="{7BD9F0C1-6F50-409D-8E77-76062676D3EC}"/>
+    <hyperlink ref="I21" r:id="rId12" xr:uid="{437E220B-63F3-4E00-844A-7CF1B055C39A}"/>
+    <hyperlink ref="J23" r:id="rId13" xr:uid="{273DDD2C-2A65-4892-8D7B-DAB407A1825C}"/>
+    <hyperlink ref="I23" r:id="rId14" xr:uid="{86E05EFD-83D2-4FDF-AF6A-74CD19D2E237}"/>
+    <hyperlink ref="J22" r:id="rId15" xr:uid="{5787F73E-5394-46BA-9912-DEFCCBF121E6}"/>
+    <hyperlink ref="I22" r:id="rId16" xr:uid="{AD191B46-2F27-4B87-B375-8ECF2EF3C755}"/>
+    <hyperlink ref="J16" r:id="rId17" xr:uid="{D49906F2-6461-45DC-BEF0-00E180454F5D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
--- a/spark-cv/data/research.xlsx
+++ b/spark-cv/data/research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97242509-7937-4265-860A-075ABC3404F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006FFDF1-A4E2-4B64-BE54-BF15FB0B96D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22800" yWindow="0" windowWidth="28800" windowHeight="21150" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23790" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>teaching</t>
   </si>
   <si>
-    <t>Created lesson plans and trained people on software programs like Excel, Word, Access, Outlook, and PowerPoint by doing hands-on demonstrations and providing one-on-one application support.</t>
-  </si>
-  <si>
     <t>Provided undergraduate students with a broad introduction into 2-dimensional and 3-dimensional Computer-Aided Design (CAD) with a focus on construction and architecture-specific applications including environmental infrastructure</t>
   </si>
   <si>
@@ -321,6 +318,9 @@
   </si>
   <si>
     <t>Developed modelling frameworks for parameter estimation, sensitivity and uncertainty analysis on integrated hydrological models</t>
+  </si>
+  <si>
+    <t>Developed and implemented lesson plans encompassing software programs such as Excel, Word, Access, Outlook, and PowerPoint through hands-on demonstrations and personalized support</t>
   </si>
 </sst>
 </file>
@@ -377,7 +377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -398,9 +398,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -740,7 +737,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -758,7 +755,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>2</v>
@@ -770,15 +767,15 @@
         <v>16</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -793,15 +790,15 @@
         <v>2013</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -816,7 +813,7 @@
         <v>2013</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>10</v>
@@ -824,7 +821,7 @@
     </row>
     <row r="6" spans="1:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -839,7 +836,7 @@
         <v>2022</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>11</v>
@@ -850,7 +847,7 @@
     </row>
     <row r="7" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -868,13 +865,13 @@
         <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:14" ht="63" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -897,7 +894,7 @@
     </row>
     <row r="9" spans="1:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -915,12 +912,12 @@
         <v>26</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -938,12 +935,12 @@
         <v>27</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -961,7 +958,7 @@
         <v>28</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="31.5" x14ac:dyDescent="0.25">
@@ -972,7 +969,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -982,13 +979,13 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="I13" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J13" s="4"/>
     </row>
@@ -1000,7 +997,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
@@ -1018,10 +1015,10 @@
         <v>25</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1034,7 +1031,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -1052,7 +1049,7 @@
         <v>25</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -1065,7 +1062,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -1077,19 +1074,19 @@
         <v>2017</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L16" s="5"/>
     </row>
@@ -1098,130 +1095,130 @@
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
     </row>
-    <row r="18" spans="1:14" s="8" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:14" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="C18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="2">
         <v>2023</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>81</v>
+      <c r="G18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:14" s="8" customFormat="1" ht="63" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:14" ht="63" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="8">
+      <c r="C19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="2">
         <v>2023</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>80</v>
+      <c r="G19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L19" s="5"/>
-      <c r="M19" s="8" t="s">
+      <c r="M19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N19" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="N19" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" s="8" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:14" ht="63" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="C20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="2">
         <v>3</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="2">
         <v>2021</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>79</v>
+      <c r="G20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
         <v>12</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="8" t="s">
-        <v>84</v>
+      <c r="M20" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="8" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="8">
+      <c r="B21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="2">
         <v>4</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="2">
         <v>2023</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="2">
         <v>2023</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="8" t="s">
+      <c r="G21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L21" s="5"/>
     </row>
@@ -1233,9 +1230,9 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="8">
+        <v>72</v>
+      </c>
+      <c r="D22" s="2">
         <v>5</v>
       </c>
       <c r="E22" s="2">
@@ -1248,10 +1245,10 @@
         <v>23</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L22" s="5"/>
     </row>
@@ -1263,9 +1260,9 @@
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="8">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2">
         <v>6</v>
       </c>
       <c r="E23" s="2">
@@ -1275,16 +1272,16 @@
         <v>2023</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L23" s="5"/>
     </row>
@@ -1296,9 +1293,9 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="8">
+        <v>71</v>
+      </c>
+      <c r="D24" s="2">
         <v>7</v>
       </c>
       <c r="E24" s="2">
@@ -1314,13 +1311,13 @@
         <v>24</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L24" s="5"/>
     </row>
@@ -1337,7 +1334,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
@@ -1369,7 +1366,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -1381,16 +1378,16 @@
         <v>2023</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="K27" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="L27" s="5"/>
     </row>
@@ -1402,7 +1399,7 @@
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
@@ -1414,16 +1411,16 @@
         <v>2021</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L28" s="5"/>
     </row>
@@ -1435,7 +1432,7 @@
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -1447,16 +1444,16 @@
         <v>2021</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L29" s="5"/>
     </row>
@@ -1477,7 +1474,7 @@
         <v>2012</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="63" x14ac:dyDescent="0.25">
@@ -1497,10 +1494,10 @@
         <v>2006</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
@@ -1520,10 +1517,10 @@
         <v>2006</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/spark-cv/data/research.xlsx
+++ b/spark-cv/data/research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006FFDF1-A4E2-4B64-BE54-BF15FB0B96D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A256475-5325-424B-8C7C-550F9806A187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23790" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
+    <workbookView xWindow="0" yWindow="1905" windowWidth="28800" windowHeight="15960" xr2:uid="{F4143829-AF9E-244C-8EFD-6252778B5E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -787,7 +787,7 @@
         <v>2020</v>
       </c>
       <c r="F4" s="2">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>91</v>
@@ -810,7 +810,7 @@
         <v>2020</v>
       </c>
       <c r="F5" s="2">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>92</v>
@@ -1004,9 +1004,6 @@
       </c>
       <c r="E14" s="1">
         <v>2020</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2023</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>31</v>
